--- a/stories/arbres/ATOM-SAN.SOM.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la maison est calme. Maman dit : c'est l'heure. Inès met son pyjama. Le pyjama est doux. Papa ouvre le lit. Inès se couche. Elle pose la tête sur l'oreiller. Papa raconte une petite histoire. Inès écoute. Elle ferme les yeux. C'est l'heure du dodo. Maman dit : le corps a besoin de dormir. Inès respire doucement. Papa baisse la lumière. Inès est au lit. C'est le dodo.</t>
+          <t>Le soir, la maison est calme. C'est l'heure. Inès met son pyjama. Le pyjama est doux. Papa ouvre le lit. Inès se couche. Elle pose la tête sur l'oreiller. Papa raconte une petite histoire. Inès écoute. Elle ferme les yeux. C'est l'heure du dodo. Le corps a besoin de dormir. Inès respire doucement. Papa baisse la lumière. Inès est au lit. C'est le dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, la maison est calme.
+maman|C'est l'heure.
+narrateur|Inès met son pyjama. Le pyjama est doux. Papa ouvre le lit. Inès se couche. Elle pose la tête sur l'oreiller. Papa raconte une petite histoire. Inès écoute. Elle ferme les yeux. C'est l'heure du dodo.
+maman|Le corps a besoin de dormir.
+narrateur|Inès respire doucement. Papa baisse la lumière. Inès est au lit. C'est le dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va dormir. Que met-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Inès dort. Le pyjama est chaud. La chambre est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Inès respire doucement. Papa baisse la lumière. Inès est au lit. C'est le dodo.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Inès va dormir. Que met-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Inès a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Inès dort. Le pyjama est chaud. La chambre est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.SOM.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le pyjama d'Inès</t>
+          <t>Le doudou sur l'oreiller</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La lampe fait un rond jaune. Le doudou attend sur l'oreiller. Victorina met le pyjama. Puis c'est le dodo.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la maison est calme. C'est l'heure. Inès met son pyjama. Le pyjama est doux. Papa ouvre le lit. Inès se couche. Elle pose la tête sur l'oreiller. Papa raconte une petite histoire. Inès écoute. Elle ferme les yeux. C'est l'heure du dodo. Le corps a besoin de dormir. Inès respire doucement. Papa baisse la lumière. Inès est au lit. C'est le dodo.</t>
+          <t>La lampe fait un rond. Le rond est jaune. Il est sur le mur. La maison sent le savon. Un grillon chante, dehors. Les volets sentent le bois. Le tapis est doux, un peu épais. Le doudou attend. Il est sur l'oreiller. L'oreiller est tout blanc. Victorina vit ici. Avec papa et maman. Victorina, tu vois le rond ? Oui, maman. Il est jaune. C'est la lampe. Un petit soleil, sur le mur. En ce moment, le soir arrive. Les volets sont fermés. La rue devient calme. Tu entends le grillon ? Oui. Il chante. C'est l'heure. On met le pyjama. Le pyjama ? Oui. Le pyjama doux. Maman tend le pyjama. Il est bleu, tout doux. Il sent le savon. Ça sent bon. Oui. Ça sent le savon. Tu mets le pantalon ? Victorina enfile le pantalon. Le coton est chaud. Elle tire un peu. Tu mets le haut ? Elle enfile le haut. Le col est tout doux. Il est doux, papa. Oui. Bravo. Tu as mis le pyjama ? Oui, maman. Bravo, Victorina. Tu as fait du bon travail. Papa ouvre le lit. Le drap est frais. Il sent le propre. Tu te couches ? Victorina se couche. Elle glisse les pieds. Elle pose la tête. L'oreiller est moelleux. Le doudou est contre sa joue. Le doudou m'attendait. Oui. Il t'attendait. Une petite histoire ? Oui, papa. Papa raconte une histoire. C'est une histoire courte. Victorina écoute. Sa main tient le doudou. Ses yeux se ferment. C'est l'heure du dodo. Le corps a besoin de dormir. Dodo, maman. Oui. Dodo. Victorina respire doucement. Papa baisse la lumière. Le rond jaune devient petit. Victorina est au lit. C'est le dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,90 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, la maison est calme.
+          <t>narrateur|La lampe fait un rond.
+narrateur|Le rond est jaune.
+narrateur|Il est sur le mur.
+narrateur|La maison sent le savon.
+narrateur|Un grillon chante, dehors.
+narrateur|Les volets sentent le bois.
+narrateur|Le tapis est doux, un peu épais.
+narrateur|Le doudou attend.
+narrateur|Il est sur l'oreiller.
+narrateur|L'oreiller est tout blanc.
+narrateur|Victorina vit ici.
+narrateur|Avec papa et maman.
+maman|Victorina, tu vois le rond ?
+enfant-f|Oui, maman.
+enfant-f|Il est jaune.
+papa|C'est la lampe.
+papa|Un petit soleil, sur le mur.
+narrateur|En ce moment, le soir arrive.
+narrateur|Les volets sont fermés.
+narrateur|La rue devient calme.
+maman|Tu entends le grillon ?
+enfant-f|Oui.
+enfant-f|Il chante.
 maman|C'est l'heure.
-narrateur|Inès met son pyjama. Le pyjama est doux. Papa ouvre le lit. Inès se couche. Elle pose la tête sur l'oreiller. Papa raconte une petite histoire. Inès écoute. Elle ferme les yeux. C'est l'heure du dodo.
+maman|On met le pyjama.
+enfant-f|Le pyjama ?
+maman|Oui.
+maman|Le pyjama doux.
+narrateur|Maman tend le pyjama.
+narrateur|Il est bleu, tout doux.
+narrateur|Il sent le savon.
+enfant-f|Ça sent bon.
+papa|Oui.
+papa|Ça sent le savon.
+papa|Tu mets le pantalon ?
+narrateur|Victorina enfile le pantalon.
+narrateur|Le coton est chaud.
+narrateur|Elle tire un peu.
+papa|Tu mets le haut ?
+narrateur|Elle enfile le haut.
+narrateur|Le col est tout doux.
+enfant-f|Il est doux, papa.
+papa|Oui.
+papa|Bravo.
+maman|Tu as mis le pyjama ?
+enfant-f|Oui, maman.
+maman|Bravo, Victorina.
+maman|Tu as fait du bon travail.
+narrateur|Papa ouvre le lit.
+narrateur|Le drap est frais.
+narrateur|Il sent le propre.
+papa|Tu te couches ?
+narrateur|Victorina se couche.
+narrateur|Elle glisse les pieds.
+narrateur|Elle pose la tête.
+narrateur|L'oreiller est moelleux.
+narrateur|Le doudou est contre sa joue.
+enfant-f|Le doudou m'attendait.
+maman|Oui.
+maman|Il t'attendait.
+papa|Une petite histoire ?
+enfant-f|Oui, papa.
+narrateur|Papa raconte une histoire.
+narrateur|C'est une histoire courte.
+narrateur|Victorina écoute.
+narrateur|Sa main tient le doudou.
+narrateur|Ses yeux se ferment.
+maman|C'est l'heure du dodo.
 maman|Le corps a besoin de dormir.
-narrateur|Inès respire doucement. Papa baisse la lumière. Inès est au lit. C'est le dodo.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|Dodo, maman.
+papa|Oui.
+papa|Dodo.
+narrateur|Victorina respire doucement.
+narrateur|Papa baisse la lumière.
+narrateur|Le rond jaune devient petit.
+narrateur|Victorina est au lit.
+narrateur|C'est le dodo.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>grillon,lampe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1432,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Inès va dormir. Que met-elle ?</t>
+          <t>Victorina va dormir. Que met-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1588,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Inès va dormir. Que met-elle ?</t>
+          <t>narrateur|Victorina va dormir.
+narrateur|Que met-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1617,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo. Papa et maman sont là.</t>
+          <t>Victorina a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo. Tu as mis le pyjama ? Oui. Le pyjama. Bravo, Victorina. Tu as fait du bon travail. Le doudou reste contre sa joue. La chambre est calme. Tu es bien au lit ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1761,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Inès a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo. Papa et maman sont là.</t>
+          <t>narrateur|Victorina a mis le pyjama.
+narrateur|Elle s'est couchée.
+narrateur|Le soir, c'est le dodo.
+maman|Tu as mis le pyjama ?
+enfant-f|Oui.
+enfant-f|Le pyjama.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+narrateur|Le doudou reste contre sa joue.
+narrateur|La chambre est calme.
+maman|Tu es bien au lit ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1800,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Inès dort. Le pyjama est chaud. La chambre est calme.</t>
+          <t>Victorina dort. Le pyjama est chaud. La chambre est calme. Tu entends encore le grillon ? Un peu. Il chante tout doux. Bravo. Le grillon chante encore. Le rond jaune est tout petit. Le tapis n'a plus de pas. Bonne nuit. Bonne nuit.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1940,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Inès dort. Le pyjama est chaud. La chambre est calme.</t>
+          <t>narrateur|Victorina dort.
+narrateur|Le pyjama est chaud.
+narrateur|La chambre est calme.
+papa|Tu entends encore le grillon ?
+enfant-f|Un peu.
+maman|Il chante tout doux.
+papa|Bravo.
+narrateur|Le grillon chante encore.
+narrateur|Le rond jaune est tout petit.
+narrateur|Le tapis n'a plus de pas.
+maman|Bonne nuit.
+enfant-f|Bonne nuit.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1979,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. C'est le dodo. Bravo. Tu as fait du bon travail. Le doudou reste sur l'oreiller. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2119,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai mis le pyjama.
+enfant-f|C'est le dodo.
+maman|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le doudou reste sur l'oreiller.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2184,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La lampe fait un rond. Le rond est jaune. Il est sur le mur. La maison sent le savon. Un grillon chante, dehors. Les volets sentent le bois. Le tapis est doux, un peu épais. Le doudou attend. Il est sur l'oreiller. L'oreiller est tout blanc. Victorina vit ici. Avec papa et maman. Victorina, tu vois le rond ? Oui, maman. Il est jaune. C'est la lampe. Un petit soleil, sur le mur. En ce moment, le soir arrive. Les volets sont fermés. La rue devient calme. Tu entends le grillon ? Oui. Il chante. C'est l'heure. On met le pyjama. Le pyjama ? Oui. Le pyjama doux. Maman tend le pyjama. Il est bleu, tout doux. Il sent le savon. Ça sent bon. Oui. Ça sent le savon. Tu mets le pantalon ? Victorina enfile le pantalon. Le coton est chaud. Elle tire un peu. Tu mets le haut ? Elle enfile le haut. Le col est tout doux. Il est doux, papa. Oui. Bravo. Tu as mis le pyjama ? Oui, maman. Bravo, Victorina. Tu as fait du bon travail. Papa ouvre le lit. Le drap est frais. Il sent le propre. Tu te couches ? Victorina se couche. Elle glisse les pieds. Elle pose la tête. L'oreiller est moelleux. Le doudou est contre sa joue. Le doudou m'attendait. Oui. Il t'attendait. Une petite histoire ? Oui, papa. Papa raconte une histoire. C'est une histoire courte. Victorina écoute. Sa main tient le doudou. Ses yeux se ferment. C'est l'heure du dodo. Le corps a besoin de dormir. Dodo, maman. Oui. Dodo. Victorina respire doucement. Papa baisse la lumière. Le rond jaune devient petit. Victorina est au lit. C'est le dodo.</t>
+          <t>La lampe fait un rond. Le rond est jaune. Il est sur le mur. La maison sent le savon. Un grillon chante, dehors. Les volets sentent le bois. Le tapis est doux, un peu épais. Le doudou attend. Il est sur l'oreiller. L'oreiller est tout blanc. Victorina vit ici. Avec papa et maman. Victorina, tu vois le rond ? Oui, maman. Il est jaune. C'est la lampe. Un petit soleil, sur le mur. En ce moment, le soir arrive. Les volets sont fermés. La rue devient calme. Tu entends le grillon ? Oui. Il chante. C'est l'heure. On met le pyjama. Le pyjama ? Oui. Le pyjama doux. Maman tend le pyjama. Il est bleu, tout doux. Il sent le savon. Ça sent bon. Oui. Ça sent le savon. Tu mets le pantalon ? Victorina enfile le pantalon. Le coton est chaud. Elle tire un peu. Tu mets le haut ? Elle enfile le haut. Le col est tout doux. Il est doux, papa. Oui. Bravo. Tu as mis le pyjama ? Oui, maman. Bravo, Victorina. Papa ouvre le lit. Le drap est frais. Il sent le propre. Tu te couches ? Victorina se couche. Elle glisse les pieds. Elle pose la tête. L'oreiller est moelleux. Le doudou est contre sa joue. Le doudou m'attendait. Oui. Il t'attendait. Une petite histoire ? Oui, papa. Papa raconte une histoire. C'est une histoire courte. Victorina écoute. Sa main tient le doudou. Ses yeux se ferment. C'est l'heure du dodo. Le corps a besoin de dormir. Dodo, maman. Oui. Dodo. Victorina respire doucement. Papa baisse la lumière. Le rond jaune devient petit. Victorina est au lit. C'est le dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, la maison est calme. Maman dit : c'est l'heure. Inès met son pyjama. Le pyjama est doux. Papa ouvre le lit. Inès se couche. Elle pose la tête sur l'oreiller. Papa raconte une petite histoire. Inès écoute. Elle ferme les yeux. C'est l'heure du dodo. Maman dit : le corps a besoin de dormir. Inès respire doucement. Papa baisse la lumière. Inès est au lit. C'est le dodo.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La lampe fait un rond. Le rond est jaune. Il est sur le mur. La maison sent le savon. Un grillon chante, dehors. Les volets sentent le bois. Le tapis est doux, un peu épais. Le doudou attend. Il est sur l'oreiller. L'oreiller est tout blanc. Victorina vit ici. Avec papa et maman. Victorina, tu vois le rond ? Oui, maman. Il est jaune. C'est la lampe. Un petit soleil, sur le mur. En ce moment, le soir arrive. Les volets sont fermés. La rue devient calme. Tu entends le grillon ? Oui. Il chante. C'est l'heure. On met le pyjama. Le pyjama ? Oui. Le pyjama doux. Maman tend le pyjama. Il est bleu, tout doux. Il sent le savon. Ça sent bon. Oui. Ça sent le savon. Tu mets le pantalon ? Victorina enfile le pantalon. Le coton est chaud. Elle tire un peu. Tu mets le haut ? Elle enfile le haut. Le col est tout doux. Il est doux, papa. Oui. Bravo. Tu as mis le pyjama ? Oui, maman. Bravo, Victorina. Papa ouvre le lit. Le drap est frais. Il sent le propre. Tu te couches ? Victorina se couche. Elle glisse les pieds. Elle pose la tête. L'oreiller est moelleux. Le doudou est contre sa joue. Le doudou m'attendait. Oui. Il t'attendait. Une petite histoire ? Oui, papa. Papa raconte une histoire. C'est une histoire courte. Victorina écoute. Sa main tient le doudou. Ses yeux se ferment. C'est l'heure du dodo. Le corps a besoin de dormir. Dodo, maman. Oui. Dodo. Victorina respire doucement. Papa baisse la lumière. Le rond jaune devient petit. Victorina est au lit. C'est le dodo.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1371,7 +1371,6 @@
 maman|Tu as mis le pyjama ?
 enfant-f|Oui, maman.
 maman|Bravo, Victorina.
-maman|Tu as fait du bon travail.
 narrateur|Papa ouvre le lit.
 narrateur|Le drap est frais.
 narrateur|Il sent le propre.
@@ -1437,7 +1436,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Inès va dormir. Que met-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina va dormir. Que met-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1592,7 +1591,6 @@
 narrateur|Que met-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1617,12 +1615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo. Tu as mis le pyjama ? Oui. Le pyjama. Bravo, Victorina. Tu as fait du bon travail. Le doudou reste contre sa joue. La chambre est calme. Tu es bien au lit ? Oui, maman.</t>
+          <t>Victorina a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo. Tu as mis le pyjama ? Oui. Le pyjama. Bravo, Victorina. Le doudou reste contre sa joue. La chambre est calme. Tu es bien au lit ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Inès a mis le pyjama. Elle s'est couchée. Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, c'est le dodo. Papa et maman sont là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo. Tu as mis le pyjama ? Oui. Le pyjama. Bravo, Victorina. Le doudou reste contre sa joue. La chambre est calme. Tu es bien au lit ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1768,14 +1766,12 @@
 enfant-f|Oui.
 enfant-f|Le pyjama.
 papa|Bravo, Victorina.
-papa|Tu as fait du bon travail.
 narrateur|Le doudou reste contre sa joue.
 narrateur|La chambre est calme.
 maman|Tu es bien au lit ?
 enfant-f|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1805,7 +1801,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Inès dort. Le &lt;emphasis level="moderate"&gt;pyjama&lt;/emphasis&gt; est chaud. La chambre est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina dort. Le pyjama est chaud. La chambre est calme. Tu entends encore le grillon ? Un peu. Il chante tout doux. Bravo. Le grillon chante encore. Le rond jaune est tout petit. Le tapis n'a plus de pas. Bonne nuit. Bonne nuit.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1954,7 +1950,6 @@
 enfant-f|Bonne nuit.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1979,12 +1974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai mis le pyjama. C'est le dodo. Bravo. Tu as fait du bon travail. Le doudou reste sur l'oreiller. L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. C'est le dodo. Bravo. Le doudou reste sur l'oreiller.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai mis le pyjama. C'est le dodo. Bravo. Le doudou reste sur l'oreiller.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2122,12 +2117,9 @@
           <t>enfant-f|J'ai mis le pyjama.
 enfant-f|C'est le dodo.
 maman|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le doudou reste sur l'oreiller.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le doudou reste sur l'oreiller.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2146,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2191,6 +2183,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre</t>
+          <t>chambre le soir, lampe, doudou</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inès, maman, papa</t>
+          <t>Victorina, papa, maman</t>
         </is>
       </c>
     </row>
